--- a/_data_list/BTS_List_PT.xlsx
+++ b/_data_list/BTS_List_PT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Telegram_Project\OrangeFlow_Dev\_data_list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C565092A-8788-4C86-BEA5-26F895349AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E9D3D01-E875-4CB9-AF66-D0633F473E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AA$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AB$89</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1974" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2063" uniqueCount="580">
   <si>
     <t>SITE ID</t>
   </si>
@@ -723,9 +723,6 @@
     <t>বাংলাবাজার, পিরিজপুর, কিশোরগঞ্জ</t>
   </si>
   <si>
-    <t>বাংলাবাজার, পিরিজপুর</t>
-  </si>
-  <si>
     <t>Chondrogram, Bajitpur, Kishoreganj</t>
   </si>
   <si>
@@ -777,9 +774,6 @@
     <t>হালিমপুর, বাজিতপুর, কিশোরগঞ্জ</t>
   </si>
   <si>
-    <t xml:space="preserve">হালিমপুর, </t>
-  </si>
-  <si>
     <t>Hilachia Bazar, Nikli, Kishoreganj</t>
   </si>
   <si>
@@ -849,9 +843,6 @@
     <t>পাটুলী বাজার, বাজিতপুর, কিশোরগঞ্জ</t>
   </si>
   <si>
-    <t>পাটুলী বাজার,</t>
-  </si>
-  <si>
     <t>Purankhola, Eidgah Math, Bajitpur, Kishoreganj</t>
   </si>
   <si>
@@ -1023,9 +1014,6 @@
     <t>গার্লস স্কুল রোড, মন্ত্রী বাড়ির সামনে, ভৈরব, কিশোরগঞ্জ</t>
   </si>
   <si>
-    <t>গার্লস স্কুল রোড মন্ত্রী বাড়ির সামনে</t>
-  </si>
-  <si>
     <t>Jamalpur,Bhairab,kishorganj</t>
   </si>
   <si>
@@ -1068,9 +1056,6 @@
     <t>খন্দকার মার্কেট, থানা রোড, ভৈরব, কিশোরগঞ্জ</t>
   </si>
   <si>
-    <t>খন্দকার মার্কেট থানা রোড</t>
-  </si>
-  <si>
     <t>Komolpur Bus Stand,Bhairab,Kishorganj</t>
   </si>
   <si>
@@ -1203,9 +1188,6 @@
     <t>সরদার কমপ্লেক্স, দুর্জয় মোড়, ভৈরব, কিশোরগঞ্জ।</t>
   </si>
   <si>
-    <t>সরদার কমপ্লেক্স দুর্জয় মোড়</t>
-  </si>
-  <si>
     <t>ShimulKandi Bhairab Kishoreganj</t>
   </si>
   <si>
@@ -1356,9 +1338,6 @@
     <t>হাফানিয়া, মাটিকাটা, ছায়াসুতি কুলিয়ারচর, কিশোরগঞ্জ</t>
   </si>
   <si>
-    <t>হাফানিয়া মাটিকাটা ছায়াসুতি</t>
-  </si>
-  <si>
     <t>Hazi Nagar Bazar, KuliyarChar, Kishorganj</t>
   </si>
   <si>
@@ -1455,9 +1434,6 @@
     <t>দক্ষিণ সালুয়া, ডুমারাকান্দা, কুলিয়ারচর, কিশোরগঞ্জ।</t>
   </si>
   <si>
-    <t>দক্ষিণ সালুয়া ডুমারাকান্দা</t>
-  </si>
-  <si>
     <t>Tarakandi, Ramdi, Kuliachar, Kishorgonj</t>
   </si>
   <si>
@@ -1497,13 +1473,301 @@
     <t>Urban</t>
   </si>
   <si>
-    <t>Baherbali, Humaipur, Bajitpur, Kishoreganj. Update</t>
-  </si>
-  <si>
-    <t>বাহেরবালী, হুমাইপুর, বাজিতপুর, কিশোরগঞ্জ। আপডেট</t>
-  </si>
-  <si>
-    <t>বাহেরবালী আপডেট</t>
+    <t>SHORT ADDRESS BN</t>
+  </si>
+  <si>
+    <t>বাহেরবালী</t>
+  </si>
+  <si>
+    <t>বাহেরবালী, হুমাইপুর, বাজিতপুর, কিশোরগঞ্জ।</t>
+  </si>
+  <si>
+    <t>Baherbali, Humaipur, Bajitpur, Kishoreganj.</t>
+  </si>
+  <si>
+    <t>Baherbali</t>
+  </si>
+  <si>
+    <t>Bangla bazar Kukrarai</t>
+  </si>
+  <si>
+    <t>Chondrogram</t>
+  </si>
+  <si>
+    <t>Dilalpur Bazar</t>
+  </si>
+  <si>
+    <t>Dokkhin Shorarchor</t>
+  </si>
+  <si>
+    <t>Gazaria bazaar</t>
+  </si>
+  <si>
+    <t>Halimpur</t>
+  </si>
+  <si>
+    <t>Hilachia Bazar</t>
+  </si>
+  <si>
+    <t>Jummapur</t>
+  </si>
+  <si>
+    <t>Mirzapur Gazirchor</t>
+  </si>
+  <si>
+    <t>Mothurapur</t>
+  </si>
+  <si>
+    <t>Murshiduddin Hall</t>
+  </si>
+  <si>
+    <t>Pirijpur Bazar</t>
+  </si>
+  <si>
+    <t>Patuli Bazar</t>
+  </si>
+  <si>
+    <t>Sonali Bank bhaban</t>
+  </si>
+  <si>
+    <t>Suvarampur</t>
+  </si>
+  <si>
+    <t>Tangoshaipur</t>
+  </si>
+  <si>
+    <t>Abdul Matin Bhuiyan</t>
+  </si>
+  <si>
+    <t>Akbor Nagor</t>
+  </si>
+  <si>
+    <t>Amlapara</t>
+  </si>
+  <si>
+    <t>Banga bandhu road</t>
+  </si>
+  <si>
+    <t>Boro razakata (westpara)</t>
+  </si>
+  <si>
+    <t>Chanpur</t>
+  </si>
+  <si>
+    <t>Chondiber</t>
+  </si>
+  <si>
+    <t>Ghora Kanda Mollah Bari</t>
+  </si>
+  <si>
+    <t>Ghori Marka Bari</t>
+  </si>
+  <si>
+    <t>Girls School Road</t>
+  </si>
+  <si>
+    <t>Jamalpur</t>
+  </si>
+  <si>
+    <t>Kalikaprasad</t>
+  </si>
+  <si>
+    <t>Kandor Ali Baparai Bari</t>
+  </si>
+  <si>
+    <t>Khandaker Market</t>
+  </si>
+  <si>
+    <t>Komolpur Bus Stand</t>
+  </si>
+  <si>
+    <t>Madhher char</t>
+  </si>
+  <si>
+    <t>Manikdi Porba khanda</t>
+  </si>
+  <si>
+    <t>Mirerbag</t>
+  </si>
+  <si>
+    <t>Mizan Group Steel Mills</t>
+  </si>
+  <si>
+    <t>Rajnagor Chawkbazar</t>
+  </si>
+  <si>
+    <t>Ram Shankarpur Dakshin Para</t>
+  </si>
+  <si>
+    <t>Sagaia</t>
+  </si>
+  <si>
+    <t>Sarder Complex</t>
+  </si>
+  <si>
+    <t>Sombhupur</t>
+  </si>
+  <si>
+    <t>Sreenagar (Purbo Para)</t>
+  </si>
+  <si>
+    <t>Agarpur Bazar</t>
+  </si>
+  <si>
+    <t>Barkarchar</t>
+  </si>
+  <si>
+    <t>Bazra</t>
+  </si>
+  <si>
+    <t>Chhaysuti</t>
+  </si>
+  <si>
+    <t>Daira khandi</t>
+  </si>
+  <si>
+    <t>Dhupkhali</t>
+  </si>
+  <si>
+    <t>Dumrakanda Bazar</t>
+  </si>
+  <si>
+    <t>East Gailkata</t>
+  </si>
+  <si>
+    <t>Foridpur Anondobazar</t>
+  </si>
+  <si>
+    <t>Hazi Nagar Bazar</t>
+  </si>
+  <si>
+    <t>Jamia Arabia Nurul-Alam Madrasa</t>
+  </si>
+  <si>
+    <t>Konapara (Chomuribazar)</t>
+  </si>
+  <si>
+    <t>Mr. Huda Kuliarchar</t>
+  </si>
+  <si>
+    <t>Near Agarpur Bus Stand</t>
+  </si>
+  <si>
+    <t>North Lakkhipur</t>
+  </si>
+  <si>
+    <t>Purbo Abdullahpur</t>
+  </si>
+  <si>
+    <t>South Salua</t>
+  </si>
+  <si>
+    <t>Banglabazar Pirijpur</t>
+  </si>
+  <si>
+    <t>হালিমপুর</t>
+  </si>
+  <si>
+    <t>বাংলাবাজার পিরিজপুর</t>
+  </si>
+  <si>
+    <t>পাটুলী বাজার</t>
+  </si>
+  <si>
+    <t>Giyanpur Chowrasta</t>
+  </si>
+  <si>
+    <t>Msher Dighi</t>
+  </si>
+  <si>
+    <t>Purankhola Eid gah Maath</t>
+  </si>
+  <si>
+    <t>Aganagor-01</t>
+  </si>
+  <si>
+    <t>Aganagor-02</t>
+  </si>
+  <si>
+    <t>Basgari</t>
+  </si>
+  <si>
+    <t>Bhairabpur Moddhopara</t>
+  </si>
+  <si>
+    <t>Bhobanipur Chawkbazar</t>
+  </si>
+  <si>
+    <t>Chondiber Hospital road</t>
+  </si>
+  <si>
+    <t>গার্লস স্কুল রোড</t>
+  </si>
+  <si>
+    <t>Kandapara</t>
+  </si>
+  <si>
+    <t>খন্দকার মার্কেট</t>
+  </si>
+  <si>
+    <t>Lundia</t>
+  </si>
+  <si>
+    <t>Milon Dori Chondiber Moor</t>
+  </si>
+  <si>
+    <t>Paratola Manikdi</t>
+  </si>
+  <si>
+    <t>Ponchoboti Notun Rasta</t>
+  </si>
+  <si>
+    <t>Ranir Bazar</t>
+  </si>
+  <si>
+    <t>Rasulpur Sadekpur</t>
+  </si>
+  <si>
+    <t>সরদার কমপ্লেক্স</t>
+  </si>
+  <si>
+    <t>ShimulKandi</t>
+  </si>
+  <si>
+    <t>South Para Lotif Road</t>
+  </si>
+  <si>
+    <t>West Noyahati Dekerchar</t>
+  </si>
+  <si>
+    <t>Endur dayer Halimpur</t>
+  </si>
+  <si>
+    <t>Mirza Nurul Haque Ujanchar</t>
+  </si>
+  <si>
+    <t>Hafania Matikata</t>
+  </si>
+  <si>
+    <t>হাফানিয়া মাটিকাটা</t>
+  </si>
+  <si>
+    <t>Jafrabad Laxmipur</t>
+  </si>
+  <si>
+    <t>Kapashatia Osmanpur</t>
+  </si>
+  <si>
+    <t>Maskandi Mor Osmanpur</t>
+  </si>
+  <si>
+    <t>দক্ষিণ সালুয়া</t>
+  </si>
+  <si>
+    <t>Tarakandi Ramdi</t>
+  </si>
+  <si>
+    <t>Upzila Road</t>
   </si>
 </sst>
 </file>
@@ -1875,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA89"/>
+  <dimension ref="A1:AB89"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -1895,15 +2159,16 @@
     <col min="15" max="15" width="61" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="65.140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="36.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="12" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="14" style="3" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="36.28515625" customWidth="1"/>
+    <col min="19" max="20" width="12" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="14" style="3" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1956,37 +2221,40 @@
         <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>27</v>
       </c>
@@ -2030,46 +2298,49 @@
         <v>220</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="R2" s="4">
+        <v>485</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="S2" s="4">
         <v>90.968151000000006</v>
       </c>
-      <c r="S2" s="4">
+      <c r="T2" s="4">
         <v>24.203620000000001</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W2" s="5">
+      <c r="X2" s="5">
         <v>44354</v>
       </c>
-      <c r="X2" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="Y2" s="5">
+      <c r="Y2" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="Z2" s="5">
         <v>44354</v>
       </c>
-      <c r="Z2" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA2" s="4" t="s">
-        <v>484</v>
+        <v>475</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>40</v>
       </c>
@@ -2119,38 +2390,41 @@
         <v>225</v>
       </c>
       <c r="Q3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="R3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="R3" s="4">
+      <c r="S3" s="4">
         <v>90.891419999999997</v>
       </c>
-      <c r="S3" s="4">
+      <c r="T3" s="4">
         <v>24.225850000000001</v>
       </c>
-      <c r="T3" s="4" t="s">
+      <c r="U3" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U3" s="4" t="s">
+      <c r="V3" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V3" s="4" t="s">
+      <c r="W3" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W3" s="5">
+      <c r="X3" s="5">
         <v>40386</v>
       </c>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5">
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5">
         <v>43782</v>
       </c>
-      <c r="Z3" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA3" s="4" t="s">
-        <v>484</v>
+        <v>475</v>
+      </c>
+      <c r="AB3" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>42</v>
       </c>
@@ -2200,38 +2474,41 @@
         <v>227</v>
       </c>
       <c r="Q4" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="R4" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="R4" s="4">
+      <c r="S4" s="4">
         <v>90.958020000000005</v>
       </c>
-      <c r="S4" s="4">
+      <c r="T4" s="4">
         <v>24.237300000000001</v>
       </c>
-      <c r="T4" s="4" t="s">
+      <c r="U4" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U4" s="4" t="s">
+      <c r="V4" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V4" s="4" t="s">
+      <c r="W4" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W4" s="5">
+      <c r="X4" s="5">
         <v>42332</v>
       </c>
-      <c r="X4" s="5"/>
-      <c r="Y4" s="5">
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="5">
         <v>43795</v>
       </c>
-      <c r="Z4" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA4" s="4" t="s">
-        <v>485</v>
+        <v>475</v>
+      </c>
+      <c r="AB4" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>44</v>
       </c>
@@ -2281,38 +2558,41 @@
         <v>230</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="R5" s="4">
+        <v>544</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="S5" s="4">
         <v>90.870944440000002</v>
       </c>
-      <c r="S5" s="4">
+      <c r="T5" s="4">
         <v>24.238194440000001</v>
       </c>
-      <c r="T5" s="4" t="s">
+      <c r="U5" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U5" s="4" t="s">
+      <c r="V5" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V5" s="4" t="s">
+      <c r="W5" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W5" s="5">
+      <c r="X5" s="5">
         <v>43253</v>
       </c>
-      <c r="X5" s="5"/>
-      <c r="Y5" s="5">
+      <c r="Y5" s="5"/>
+      <c r="Z5" s="5">
         <v>43863</v>
       </c>
-      <c r="Z5" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA5" s="4" t="s">
-        <v>484</v>
+        <v>475</v>
+      </c>
+      <c r="AB5" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>46</v>
       </c>
@@ -2356,44 +2636,47 @@
         <v>220</v>
       </c>
       <c r="O6" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="P6" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="P6" s="4" t="s">
+      <c r="Q6" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="R6" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="Q6" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="R6" s="4">
+      <c r="S6" s="4">
         <v>90.93768</v>
       </c>
-      <c r="S6" s="4">
+      <c r="T6" s="4">
         <v>24.205380000000002</v>
       </c>
-      <c r="T6" s="4" t="s">
+      <c r="U6" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U6" s="4" t="s">
+      <c r="V6" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V6" s="4" t="s">
+      <c r="W6" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W6" s="5">
+      <c r="X6" s="5">
         <v>39720</v>
       </c>
-      <c r="X6" s="5"/>
-      <c r="Y6" s="5">
+      <c r="Y6" s="5"/>
+      <c r="Z6" s="5">
         <v>43767</v>
       </c>
-      <c r="Z6" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA6" s="4" t="s">
-        <v>485</v>
+        <v>475</v>
+      </c>
+      <c r="AB6" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>48</v>
       </c>
@@ -2437,44 +2720,47 @@
         <v>220</v>
       </c>
       <c r="O7" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="P7" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="P7" s="4" t="s">
+      <c r="Q7" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="R7" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="Q7" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="R7" s="4">
+      <c r="S7" s="4">
         <v>90.973699999999994</v>
       </c>
-      <c r="S7" s="4">
+      <c r="T7" s="4">
         <v>24.188600000000001</v>
       </c>
-      <c r="T7" s="4" t="s">
+      <c r="U7" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U7" s="4" t="s">
+      <c r="V7" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V7" s="4" t="s">
+      <c r="W7" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W7" s="5">
+      <c r="X7" s="5">
         <v>39964</v>
       </c>
-      <c r="X7" s="5"/>
-      <c r="Y7" s="5">
+      <c r="Y7" s="5"/>
+      <c r="Z7" s="5">
         <v>43643</v>
       </c>
-      <c r="Z7" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA7" s="4" t="s">
-        <v>485</v>
+        <v>475</v>
+      </c>
+      <c r="AB7" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>50</v>
       </c>
@@ -2518,44 +2804,47 @@
         <v>220</v>
       </c>
       <c r="O8" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="P8" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="P8" s="4" t="s">
+      <c r="Q8" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="R8" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="Q8" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="R8" s="4">
+      <c r="S8" s="4">
         <v>90.896054000000007</v>
       </c>
-      <c r="S8" s="4">
+      <c r="T8" s="4">
         <v>24.207491999999998</v>
       </c>
-      <c r="T8" s="4" t="s">
+      <c r="U8" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U8" s="4" t="s">
+      <c r="V8" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V8" s="4" t="s">
+      <c r="W8" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W8" s="5">
+      <c r="X8" s="5">
         <v>44926</v>
       </c>
-      <c r="X8" s="5"/>
-      <c r="Y8" s="5">
+      <c r="Y8" s="5"/>
+      <c r="Z8" s="5">
         <v>44926</v>
       </c>
-      <c r="Z8" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA8" s="4" t="s">
-        <v>484</v>
+        <v>475</v>
+      </c>
+      <c r="AB8" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>52</v>
       </c>
@@ -2599,44 +2888,47 @@
         <v>220</v>
       </c>
       <c r="O9" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="P9" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="P9" s="4" t="s">
+      <c r="Q9" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="R9" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="Q9" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="R9" s="4">
+      <c r="S9" s="4">
         <v>90.836309999999997</v>
       </c>
-      <c r="S9" s="4">
+      <c r="T9" s="4">
         <v>24.229679999999998</v>
       </c>
-      <c r="T9" s="4" t="s">
+      <c r="U9" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U9" s="4" t="s">
+      <c r="V9" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V9" s="4" t="s">
+      <c r="W9" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W9" s="5">
+      <c r="X9" s="5">
         <v>39720</v>
       </c>
-      <c r="X9" s="5"/>
-      <c r="Y9" s="5">
+      <c r="Y9" s="5"/>
+      <c r="Z9" s="5">
         <v>43795</v>
       </c>
-      <c r="Z9" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA9" s="4" t="s">
-        <v>485</v>
+        <v>475</v>
+      </c>
+      <c r="AB9" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>54</v>
       </c>
@@ -2680,44 +2972,47 @@
         <v>220</v>
       </c>
       <c r="O10" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="P10" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="P10" s="4" t="s">
+      <c r="Q10" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="R10" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="Q10" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="R10" s="4">
+      <c r="S10" s="4">
         <v>90.904200000000003</v>
       </c>
-      <c r="S10" s="4">
+      <c r="T10" s="4">
         <v>24.242640000000002</v>
       </c>
-      <c r="T10" s="4" t="s">
+      <c r="U10" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U10" s="4" t="s">
+      <c r="V10" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V10" s="4" t="s">
+      <c r="W10" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W10" s="5">
+      <c r="X10" s="5">
         <v>41844</v>
       </c>
-      <c r="X10" s="5"/>
-      <c r="Y10" s="5">
+      <c r="Y10" s="5"/>
+      <c r="Z10" s="5">
         <v>43795</v>
       </c>
-      <c r="Z10" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA10" s="4" t="s">
-        <v>484</v>
+        <v>475</v>
+      </c>
+      <c r="AB10" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>56</v>
       </c>
@@ -2761,44 +3056,47 @@
         <v>220</v>
       </c>
       <c r="O11" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="P11" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="P11" s="4" t="s">
-        <v>248</v>
-      </c>
       <c r="Q11" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="R11" s="4">
+        <v>491</v>
+      </c>
+      <c r="R11" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="S11" s="4">
         <v>90.884979999999999</v>
       </c>
-      <c r="S11" s="4">
+      <c r="T11" s="4">
         <v>24.2537971</v>
       </c>
-      <c r="T11" s="4" t="s">
+      <c r="U11" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U11" s="4" t="s">
+      <c r="V11" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V11" s="4" t="s">
+      <c r="W11" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W11" s="5">
+      <c r="X11" s="5">
         <v>45169</v>
       </c>
-      <c r="X11" s="5"/>
-      <c r="Y11" s="5">
+      <c r="Y11" s="5"/>
+      <c r="Z11" s="5">
         <v>45169</v>
       </c>
-      <c r="Z11" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA11" s="4" t="s">
-        <v>484</v>
+        <v>475</v>
+      </c>
+      <c r="AB11" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>58</v>
       </c>
@@ -2842,44 +3140,47 @@
         <v>220</v>
       </c>
       <c r="O12" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q12" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="R12" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="P12" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="Q12" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="R12" s="4">
+      <c r="S12" s="4">
         <v>90.929670000000002</v>
       </c>
-      <c r="S12" s="4">
+      <c r="T12" s="4">
         <v>24.262039999999999</v>
       </c>
-      <c r="T12" s="4" t="s">
+      <c r="U12" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U12" s="4" t="s">
+      <c r="V12" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V12" s="4" t="s">
+      <c r="W12" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W12" s="5">
+      <c r="X12" s="5">
         <v>39772</v>
       </c>
-      <c r="X12" s="5"/>
-      <c r="Y12" s="5">
+      <c r="Y12" s="5"/>
+      <c r="Z12" s="5">
         <v>43612</v>
       </c>
-      <c r="Z12" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA12" s="4" t="s">
-        <v>485</v>
+        <v>475</v>
+      </c>
+      <c r="AB12" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>60</v>
       </c>
@@ -2923,46 +3224,49 @@
         <v>220</v>
       </c>
       <c r="O13" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="P13" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="R13" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="P13" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q13" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="R13" s="4">
+      <c r="S13" s="4">
         <v>90.924181000000004</v>
       </c>
-      <c r="S13" s="4">
+      <c r="T13" s="4">
         <v>24.216778000000001</v>
       </c>
-      <c r="T13" s="4" t="s">
+      <c r="U13" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U13" s="4" t="s">
+      <c r="V13" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V13" s="4" t="s">
+      <c r="W13" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W13" s="5">
+      <c r="X13" s="5">
         <v>44658</v>
       </c>
-      <c r="X13" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="Y13" s="5">
+      <c r="Y13" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="Z13" s="5">
         <v>44658</v>
       </c>
-      <c r="Z13" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA13" s="4" t="s">
-        <v>486</v>
+        <v>475</v>
+      </c>
+      <c r="AB13" s="4" t="s">
+        <v>478</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>62</v>
       </c>
@@ -3006,44 +3310,47 @@
         <v>220</v>
       </c>
       <c r="O14" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="P14" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q14" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="R14" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="P14" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q14" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="R14" s="4">
+      <c r="S14" s="4">
         <v>90.940380000000005</v>
       </c>
-      <c r="S14" s="4">
+      <c r="T14" s="4">
         <v>24.183440000000001</v>
       </c>
-      <c r="T14" s="4" t="s">
+      <c r="U14" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U14" s="4" t="s">
+      <c r="V14" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V14" s="4" t="s">
+      <c r="W14" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W14" s="5">
+      <c r="X14" s="5">
         <v>44309</v>
       </c>
-      <c r="X14" s="5"/>
-      <c r="Y14" s="5">
+      <c r="Y14" s="5"/>
+      <c r="Z14" s="5">
         <v>44309</v>
       </c>
-      <c r="Z14" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA14" s="4" t="s">
-        <v>484</v>
+        <v>475</v>
+      </c>
+      <c r="AB14" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>64</v>
       </c>
@@ -3087,44 +3394,47 @@
         <v>220</v>
       </c>
       <c r="O15" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="P15" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q15" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="R15" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="P15" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="Q15" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="R15" s="4">
+      <c r="S15" s="4">
         <v>90.958798000000002</v>
       </c>
-      <c r="S15" s="4">
+      <c r="T15" s="4">
         <v>24.216149000000001</v>
       </c>
-      <c r="T15" s="4" t="s">
+      <c r="U15" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U15" s="4" t="s">
+      <c r="V15" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V15" s="4" t="s">
+      <c r="W15" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W15" s="5">
+      <c r="X15" s="5">
         <v>45292</v>
       </c>
-      <c r="X15" s="5"/>
-      <c r="Y15" s="5">
+      <c r="Y15" s="5"/>
+      <c r="Z15" s="5">
         <v>45292</v>
       </c>
-      <c r="Z15" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA15" s="4" t="s">
-        <v>487</v>
+        <v>475</v>
+      </c>
+      <c r="AB15" s="4" t="s">
+        <v>479</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>66</v>
       </c>
@@ -3168,44 +3478,47 @@
         <v>220</v>
       </c>
       <c r="O16" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="P16" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q16" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="R16" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="P16" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q16" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="R16" s="4">
+      <c r="S16" s="4">
         <v>90.953258099999999</v>
       </c>
-      <c r="S16" s="4">
+      <c r="T16" s="4">
         <v>24.185290999999999</v>
       </c>
-      <c r="T16" s="4" t="s">
+      <c r="U16" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U16" s="4" t="s">
+      <c r="V16" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V16" s="4" t="s">
+      <c r="W16" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W16" s="5">
+      <c r="X16" s="5">
         <v>44739</v>
       </c>
-      <c r="X16" s="5"/>
-      <c r="Y16" s="5">
+      <c r="Y16" s="5"/>
+      <c r="Z16" s="5">
         <v>44739</v>
       </c>
-      <c r="Z16" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA16" s="4" t="s">
-        <v>486</v>
+        <v>475</v>
+      </c>
+      <c r="AB16" s="4" t="s">
+        <v>478</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>68</v>
       </c>
@@ -3249,44 +3562,47 @@
         <v>220</v>
       </c>
       <c r="O17" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q17" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="R17" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="P17" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q17" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="R17" s="4">
+      <c r="S17" s="4">
         <v>90.917050000000003</v>
       </c>
-      <c r="S17" s="4">
+      <c r="T17" s="4">
         <v>24.201070000000001</v>
       </c>
-      <c r="T17" s="4" t="s">
+      <c r="U17" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U17" s="4" t="s">
+      <c r="V17" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V17" s="4" t="s">
+      <c r="W17" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W17" s="5">
+      <c r="X17" s="5">
         <v>38711</v>
       </c>
-      <c r="X17" s="5"/>
-      <c r="Y17" s="5">
+      <c r="Y17" s="5"/>
+      <c r="Z17" s="5">
         <v>43640</v>
       </c>
-      <c r="Z17" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA17" s="4" t="s">
-        <v>485</v>
+        <v>475</v>
+      </c>
+      <c r="AB17" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>70</v>
       </c>
@@ -3330,44 +3646,47 @@
         <v>220</v>
       </c>
       <c r="O18" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="P18" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q18" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="R18" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="P18" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q18" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="R18" s="4">
+      <c r="S18" s="4">
         <v>90.853589999999997</v>
       </c>
-      <c r="S18" s="4">
+      <c r="T18" s="4">
         <v>24.21153</v>
       </c>
-      <c r="T18" s="4" t="s">
+      <c r="U18" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U18" s="4" t="s">
+      <c r="V18" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V18" s="4" t="s">
+      <c r="W18" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W18" s="5">
+      <c r="X18" s="5">
         <v>41821</v>
       </c>
-      <c r="X18" s="5"/>
-      <c r="Y18" s="5">
+      <c r="Y18" s="5"/>
+      <c r="Z18" s="5">
         <v>43795</v>
       </c>
-      <c r="Z18" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA18" s="4" t="s">
-        <v>485</v>
+        <v>475</v>
+      </c>
+      <c r="AB18" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>72</v>
       </c>
@@ -3411,46 +3730,49 @@
         <v>220</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="R19" s="4">
+        <v>498</v>
+      </c>
+      <c r="R19" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="S19" s="4">
         <v>90.980564999999999</v>
       </c>
-      <c r="S19" s="4">
+      <c r="T19" s="4">
         <v>24.230236999999999</v>
       </c>
-      <c r="T19" s="4" t="s">
+      <c r="U19" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U19" s="4" t="s">
+      <c r="V19" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V19" s="4" t="s">
+      <c r="W19" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W19" s="5">
+      <c r="X19" s="5">
         <v>45309</v>
       </c>
-      <c r="X19" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="Y19" s="5">
+      <c r="Y19" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="Z19" s="5">
         <v>45309</v>
       </c>
-      <c r="Z19" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA19" s="4" t="s">
-        <v>486</v>
+        <v>475</v>
+      </c>
+      <c r="AB19" s="4" t="s">
+        <v>478</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>74</v>
       </c>
@@ -3494,44 +3816,47 @@
         <v>220</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="R20" s="4">
+        <v>550</v>
+      </c>
+      <c r="R20" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="S20" s="4">
         <v>90.869739999999993</v>
       </c>
-      <c r="S20" s="4">
+      <c r="T20" s="4">
         <v>24.218858000000001</v>
       </c>
-      <c r="T20" s="4" t="s">
+      <c r="U20" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U20" s="4" t="s">
+      <c r="V20" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V20" s="4" t="s">
+      <c r="W20" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W20" s="5">
+      <c r="X20" s="5">
         <v>45169</v>
       </c>
-      <c r="X20" s="5"/>
-      <c r="Y20" s="5">
+      <c r="Y20" s="5"/>
+      <c r="Z20" s="5">
         <v>45169</v>
       </c>
-      <c r="Z20" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA20" s="4" t="s">
-        <v>484</v>
+        <v>475</v>
+      </c>
+      <c r="AB20" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>76</v>
       </c>
@@ -3575,44 +3900,47 @@
         <v>220</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="Q21" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="R21" s="4">
+        <v>499</v>
+      </c>
+      <c r="R21" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="S21" s="4">
         <v>90.949960000000004</v>
       </c>
-      <c r="S21" s="4">
+      <c r="T21" s="4">
         <v>24.214880000000001</v>
       </c>
-      <c r="T21" s="4" t="s">
+      <c r="U21" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U21" s="4" t="s">
+      <c r="V21" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V21" s="4" t="s">
+      <c r="W21" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W21" s="5">
+      <c r="X21" s="5">
         <v>39310</v>
       </c>
-      <c r="X21" s="5"/>
-      <c r="Y21" s="5">
+      <c r="Y21" s="5"/>
+      <c r="Z21" s="5">
         <v>43643</v>
       </c>
-      <c r="Z21" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA21" s="4" t="s">
-        <v>485</v>
+        <v>475</v>
+      </c>
+      <c r="AB21" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>78</v>
       </c>
@@ -3656,44 +3984,47 @@
         <v>220</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="R22" s="4">
+        <v>500</v>
+      </c>
+      <c r="R22" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="S22" s="4">
         <v>90.974609999999998</v>
       </c>
-      <c r="S22" s="4">
+      <c r="T22" s="4">
         <v>24.21762</v>
       </c>
-      <c r="T22" s="4" t="s">
+      <c r="U22" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U22" s="4" t="s">
+      <c r="V22" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V22" s="4" t="s">
+      <c r="W22" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W22" s="5">
+      <c r="X22" s="5">
         <v>40908</v>
       </c>
-      <c r="X22" s="5"/>
-      <c r="Y22" s="5">
+      <c r="Y22" s="5"/>
+      <c r="Z22" s="5">
         <v>43643</v>
       </c>
-      <c r="Z22" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA22" s="4" t="s">
-        <v>485</v>
+        <v>475</v>
+      </c>
+      <c r="AB22" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>80</v>
       </c>
@@ -3737,44 +4068,47 @@
         <v>220</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="R23" s="4">
+        <v>501</v>
+      </c>
+      <c r="R23" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="S23" s="4">
         <v>91.044430000000006</v>
       </c>
-      <c r="S23" s="4">
+      <c r="T23" s="4">
         <v>24.263760000000001</v>
       </c>
-      <c r="T23" s="4" t="s">
+      <c r="U23" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U23" s="4" t="s">
+      <c r="V23" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V23" s="4" t="s">
+      <c r="W23" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W23" s="5">
+      <c r="X23" s="5">
         <v>39993</v>
       </c>
-      <c r="X23" s="5"/>
-      <c r="Y23" s="5">
+      <c r="Y23" s="5"/>
+      <c r="Z23" s="5">
         <v>43797</v>
       </c>
-      <c r="Z23" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA23" s="4" t="s">
-        <v>485</v>
+        <v>475</v>
+      </c>
+      <c r="AB23" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>82</v>
       </c>
@@ -3818,44 +4152,47 @@
         <v>220</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="Q24" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="R24" s="4">
+        <v>502</v>
+      </c>
+      <c r="R24" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="S24" s="4">
         <v>90.9726</v>
       </c>
-      <c r="S24" s="4">
+      <c r="T24" s="4">
         <v>24.068999999999999</v>
       </c>
-      <c r="T24" s="4" t="s">
+      <c r="U24" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U24" s="4" t="s">
+      <c r="V24" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V24" s="4" t="s">
+      <c r="W24" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W24" s="5">
+      <c r="X24" s="5">
         <v>43342</v>
       </c>
-      <c r="X24" s="5"/>
-      <c r="Y24" s="5">
+      <c r="Y24" s="5"/>
+      <c r="Z24" s="5">
         <v>43614</v>
       </c>
-      <c r="Z24" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA24" s="4" t="s">
-        <v>485</v>
+        <v>480</v>
+      </c>
+      <c r="AB24" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>86</v>
       </c>
@@ -3899,44 +4236,47 @@
         <v>220</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="Q25" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="R25" s="4">
+        <v>551</v>
+      </c>
+      <c r="R25" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="S25" s="4">
         <v>91.027074999999996</v>
       </c>
-      <c r="S25" s="4">
+      <c r="T25" s="4">
         <v>24.087814999999999</v>
       </c>
-      <c r="T25" s="4" t="s">
+      <c r="U25" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U25" s="4" t="s">
+      <c r="V25" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V25" s="4" t="s">
+      <c r="W25" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W25" s="5">
+      <c r="X25" s="5">
         <v>44712</v>
       </c>
-      <c r="X25" s="5"/>
-      <c r="Y25" s="5">
+      <c r="Y25" s="5"/>
+      <c r="Z25" s="5">
         <v>44712</v>
       </c>
-      <c r="Z25" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA25" s="4" t="s">
-        <v>486</v>
+        <v>480</v>
+      </c>
+      <c r="AB25" s="4" t="s">
+        <v>478</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>88</v>
       </c>
@@ -3980,44 +4320,47 @@
         <v>220</v>
       </c>
       <c r="O26" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="P26" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q26" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="R26" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="P26" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q26" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="R26" s="4">
+      <c r="S26" s="4">
         <v>91.026079999999993</v>
       </c>
-      <c r="S26" s="4">
+      <c r="T26" s="4">
         <v>24.096219999999999</v>
       </c>
-      <c r="T26" s="4" t="s">
+      <c r="U26" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U26" s="4" t="s">
+      <c r="V26" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V26" s="4" t="s">
+      <c r="W26" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W26" s="5">
+      <c r="X26" s="5">
         <v>44299</v>
       </c>
-      <c r="X26" s="5"/>
-      <c r="Y26" s="5">
+      <c r="Y26" s="5"/>
+      <c r="Z26" s="5">
         <v>44299</v>
       </c>
-      <c r="Z26" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA26" s="4" t="s">
-        <v>485</v>
+        <v>480</v>
+      </c>
+      <c r="AB26" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>90</v>
       </c>
@@ -4061,44 +4404,47 @@
         <v>220</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Q27" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="R27" s="4">
+        <v>503</v>
+      </c>
+      <c r="R27" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="S27" s="4">
         <v>90.928120000000007</v>
       </c>
-      <c r="S27" s="4">
+      <c r="T27" s="4">
         <v>24.105139999999999</v>
       </c>
-      <c r="T27" s="4" t="s">
+      <c r="U27" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U27" s="4" t="s">
+      <c r="V27" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V27" s="4" t="s">
+      <c r="W27" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W27" s="5">
+      <c r="X27" s="5">
         <v>40896</v>
       </c>
-      <c r="X27" s="5"/>
-      <c r="Y27" s="5">
+      <c r="Y27" s="5"/>
+      <c r="Z27" s="5">
         <v>43640</v>
       </c>
-      <c r="Z27" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA27" s="4" t="s">
-        <v>485</v>
+        <v>480</v>
+      </c>
+      <c r="AB27" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>92</v>
       </c>
@@ -4142,44 +4488,47 @@
         <v>220</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="P28" s="4" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="Q28" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="R28" s="4">
+        <v>504</v>
+      </c>
+      <c r="R28" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="S28" s="4">
         <v>90.976298999999997</v>
       </c>
-      <c r="S28" s="4">
+      <c r="T28" s="4">
         <v>24.051033</v>
       </c>
-      <c r="T28" s="4" t="s">
+      <c r="U28" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U28" s="4" t="s">
+      <c r="V28" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V28" s="4" t="s">
+      <c r="W28" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W28" s="5">
+      <c r="X28" s="5">
         <v>45208</v>
       </c>
-      <c r="X28" s="5"/>
-      <c r="Y28" s="5">
+      <c r="Y28" s="5"/>
+      <c r="Z28" s="5">
         <v>45208</v>
       </c>
-      <c r="Z28" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA28" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
+      </c>
+      <c r="AB28" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>94</v>
       </c>
@@ -4223,44 +4572,47 @@
         <v>220</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="P29" s="4" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="Q29" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="R29" s="4">
+        <v>505</v>
+      </c>
+      <c r="R29" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="S29" s="4">
         <v>90.98621</v>
       </c>
-      <c r="S29" s="4">
+      <c r="T29" s="4">
         <v>24.046900000000001</v>
       </c>
-      <c r="T29" s="4" t="s">
+      <c r="U29" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U29" s="4" t="s">
+      <c r="V29" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V29" s="4" t="s">
+      <c r="W29" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W29" s="5">
+      <c r="X29" s="5">
         <v>39164</v>
       </c>
-      <c r="X29" s="5"/>
-      <c r="Y29" s="5">
+      <c r="Y29" s="5"/>
+      <c r="Z29" s="5">
         <v>43797</v>
       </c>
-      <c r="Z29" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA29" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
+      </c>
+      <c r="AB29" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>96</v>
       </c>
@@ -4304,44 +4656,47 @@
         <v>220</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="P30" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="Q30" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="R30" s="4">
+        <v>553</v>
+      </c>
+      <c r="R30" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="S30" s="4">
         <v>90.954329999999999</v>
       </c>
-      <c r="S30" s="4">
+      <c r="T30" s="4">
         <v>24.102959999999999</v>
       </c>
-      <c r="T30" s="4" t="s">
+      <c r="U30" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U30" s="4" t="s">
+      <c r="V30" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V30" s="4" t="s">
+      <c r="W30" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W30" s="5">
+      <c r="X30" s="5">
         <v>44742</v>
       </c>
-      <c r="X30" s="5"/>
-      <c r="Y30" s="5">
+      <c r="Y30" s="5"/>
+      <c r="Z30" s="5">
         <v>44742</v>
       </c>
-      <c r="Z30" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA30" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
+      </c>
+      <c r="AB30" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>98</v>
       </c>
@@ -4385,44 +4740,47 @@
         <v>220</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="Q31" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="R31" s="4">
+        <v>554</v>
+      </c>
+      <c r="R31" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="S31" s="4">
         <v>90.982929999999996</v>
       </c>
-      <c r="S31" s="4">
+      <c r="T31" s="4">
         <v>24.059439999999999</v>
       </c>
-      <c r="T31" s="4" t="s">
+      <c r="U31" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U31" s="4" t="s">
+      <c r="V31" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V31" s="4" t="s">
+      <c r="W31" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W31" s="5">
+      <c r="X31" s="5">
         <v>45412</v>
       </c>
-      <c r="X31" s="5"/>
-      <c r="Y31" s="5">
+      <c r="Y31" s="5"/>
+      <c r="Z31" s="5">
         <v>45412</v>
       </c>
-      <c r="Z31" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA31" s="4" t="s">
-        <v>487</v>
+        <v>480</v>
+      </c>
+      <c r="AB31" s="4" t="s">
+        <v>479</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>100</v>
       </c>
@@ -4466,44 +4824,47 @@
         <v>220</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="Q32" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="R32" s="4">
+        <v>555</v>
+      </c>
+      <c r="R32" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="S32" s="4">
         <v>90.977450000000005</v>
       </c>
-      <c r="S32" s="4">
+      <c r="T32" s="4">
         <v>24.11561</v>
       </c>
-      <c r="T32" s="4" t="s">
+      <c r="U32" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U32" s="4" t="s">
+      <c r="V32" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V32" s="4" t="s">
+      <c r="W32" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W32" s="5">
+      <c r="X32" s="5">
         <v>40117</v>
       </c>
-      <c r="X32" s="5"/>
-      <c r="Y32" s="5">
+      <c r="Y32" s="5"/>
+      <c r="Z32" s="5">
         <v>43643</v>
       </c>
-      <c r="Z32" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA32" s="4" t="s">
-        <v>485</v>
+        <v>480</v>
+      </c>
+      <c r="AB32" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>102</v>
       </c>
@@ -4547,44 +4908,47 @@
         <v>220</v>
       </c>
       <c r="O33" s="4" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="P33" s="4" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="Q33" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="R33" s="4">
+        <v>506</v>
+      </c>
+      <c r="R33" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="S33" s="4">
         <v>90.992323999999996</v>
       </c>
-      <c r="S33" s="4">
+      <c r="T33" s="4">
         <v>24.085882999999999</v>
       </c>
-      <c r="T33" s="4" t="s">
+      <c r="U33" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U33" s="4" t="s">
+      <c r="V33" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V33" s="4" t="s">
+      <c r="W33" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W33" s="5">
+      <c r="X33" s="5">
         <v>44819</v>
       </c>
-      <c r="X33" s="5"/>
-      <c r="Y33" s="5">
+      <c r="Y33" s="5"/>
+      <c r="Z33" s="5">
         <v>44819</v>
       </c>
-      <c r="Z33" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA33" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
+      </c>
+      <c r="AB33" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>104</v>
       </c>
@@ -4628,44 +4992,47 @@
         <v>220</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="Q34" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="R34" s="4">
+        <v>507</v>
+      </c>
+      <c r="R34" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="S34" s="4">
         <v>91.003088000000005</v>
       </c>
-      <c r="S34" s="4">
+      <c r="T34" s="4">
         <v>24.079201000000001</v>
       </c>
-      <c r="T34" s="4" t="s">
+      <c r="U34" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U34" s="4" t="s">
+      <c r="V34" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V34" s="4" t="s">
+      <c r="W34" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W34" s="5">
+      <c r="X34" s="5">
         <v>45169</v>
       </c>
-      <c r="X34" s="5"/>
-      <c r="Y34" s="5">
+      <c r="Y34" s="5"/>
+      <c r="Z34" s="5">
         <v>45169</v>
       </c>
-      <c r="Z34" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA34" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
+      </c>
+      <c r="AB34" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>106</v>
       </c>
@@ -4709,44 +5076,47 @@
         <v>220</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="Q35" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="R35" s="4">
+        <v>556</v>
+      </c>
+      <c r="R35" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="S35" s="4">
         <v>90.987440000000007</v>
       </c>
-      <c r="S35" s="4">
+      <c r="T35" s="4">
         <v>24.062200000000001</v>
       </c>
-      <c r="T35" s="4" t="s">
+      <c r="U35" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U35" s="4" t="s">
+      <c r="V35" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V35" s="4" t="s">
+      <c r="W35" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W35" s="5">
+      <c r="X35" s="5">
         <v>44187</v>
       </c>
-      <c r="X35" s="5"/>
-      <c r="Y35" s="5">
+      <c r="Y35" s="5"/>
+      <c r="Z35" s="5">
         <v>44187</v>
       </c>
-      <c r="Z35" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA35" s="4" t="s">
-        <v>485</v>
+        <v>480</v>
+      </c>
+      <c r="AB35" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>108</v>
       </c>
@@ -4790,44 +5160,47 @@
         <v>220</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="Q36" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="R36" s="4">
+        <v>508</v>
+      </c>
+      <c r="R36" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="S36" s="4">
         <v>90.991190000000003</v>
       </c>
-      <c r="S36" s="4">
+      <c r="T36" s="4">
         <v>24.056719999999999</v>
       </c>
-      <c r="T36" s="4" t="s">
+      <c r="U36" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U36" s="4" t="s">
+      <c r="V36" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V36" s="4" t="s">
+      <c r="W36" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W36" s="5">
+      <c r="X36" s="5">
         <v>45214</v>
       </c>
-      <c r="X36" s="5"/>
-      <c r="Y36" s="5">
+      <c r="Y36" s="5"/>
+      <c r="Z36" s="5">
         <v>45214</v>
       </c>
-      <c r="Z36" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA36" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
+      </c>
+      <c r="AB36" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>110</v>
       </c>
@@ -4871,44 +5244,47 @@
         <v>220</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="P37" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="Q37" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="R37" s="4">
+        <v>509</v>
+      </c>
+      <c r="R37" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="S37" s="4">
         <v>90.983609999999999</v>
       </c>
-      <c r="S37" s="4">
+      <c r="T37" s="4">
         <v>24.044370000000001</v>
       </c>
-      <c r="T37" s="4" t="s">
+      <c r="U37" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U37" s="4" t="s">
+      <c r="V37" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V37" s="4" t="s">
+      <c r="W37" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W37" s="5">
+      <c r="X37" s="5">
         <v>40815</v>
       </c>
-      <c r="X37" s="5"/>
-      <c r="Y37" s="5">
+      <c r="Y37" s="5"/>
+      <c r="Z37" s="5">
         <v>43642</v>
       </c>
-      <c r="Z37" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA37" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
+      </c>
+      <c r="AB37" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>112</v>
       </c>
@@ -4952,44 +5328,47 @@
         <v>220</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="Q38" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="R38" s="4">
+        <v>510</v>
+      </c>
+      <c r="R38" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="S38" s="4">
         <v>90.992999999999995</v>
       </c>
-      <c r="S38" s="4">
+      <c r="T38" s="4">
         <v>24.052399999999999</v>
       </c>
-      <c r="T38" s="4" t="s">
+      <c r="U38" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U38" s="4" t="s">
+      <c r="V38" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V38" s="4" t="s">
+      <c r="W38" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W38" s="5">
+      <c r="X38" s="5">
         <v>43270</v>
       </c>
-      <c r="X38" s="5"/>
-      <c r="Y38" s="5">
+      <c r="Y38" s="5"/>
+      <c r="Z38" s="5">
         <v>43795</v>
       </c>
-      <c r="Z38" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA38" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
+      </c>
+      <c r="AB38" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>114</v>
       </c>
@@ -5033,44 +5412,47 @@
         <v>220</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="P39" s="4" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="Q39" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="R39" s="4">
+        <v>511</v>
+      </c>
+      <c r="R39" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="S39" s="4">
         <v>90.984390000000005</v>
       </c>
-      <c r="S39" s="4">
+      <c r="T39" s="4">
         <v>24.05171</v>
       </c>
-      <c r="T39" s="4" t="s">
+      <c r="U39" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U39" s="4" t="s">
+      <c r="V39" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V39" s="4" t="s">
+      <c r="W39" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W39" s="5">
+      <c r="X39" s="5">
         <v>39895</v>
       </c>
-      <c r="X39" s="5"/>
-      <c r="Y39" s="5">
+      <c r="Y39" s="5"/>
+      <c r="Z39" s="5">
         <v>43640</v>
       </c>
-      <c r="Z39" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA39" s="4" t="s">
-        <v>485</v>
+        <v>480</v>
+      </c>
+      <c r="AB39" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>116</v>
       </c>
@@ -5114,44 +5496,47 @@
         <v>220</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="Q40" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="R40" s="4">
+        <v>512</v>
+      </c>
+      <c r="R40" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="S40" s="4">
         <v>90.958600000000004</v>
       </c>
-      <c r="S40" s="4">
+      <c r="T40" s="4">
         <v>24.091229999999999</v>
       </c>
-      <c r="T40" s="4" t="s">
+      <c r="U40" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U40" s="4" t="s">
+      <c r="V40" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V40" s="4" t="s">
+      <c r="W40" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W40" s="5">
+      <c r="X40" s="5">
         <v>44165</v>
       </c>
-      <c r="X40" s="5"/>
-      <c r="Y40" s="5">
+      <c r="Y40" s="5"/>
+      <c r="Z40" s="5">
         <v>44165</v>
       </c>
-      <c r="Z40" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA40" s="4" t="s">
-        <v>485</v>
+        <v>480</v>
+      </c>
+      <c r="AB40" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>118</v>
       </c>
@@ -5195,44 +5580,47 @@
         <v>220</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="P41" s="4" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="Q41" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="R41" s="4">
+        <v>513</v>
+      </c>
+      <c r="R41" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="S41" s="4">
         <v>90.937899999999999</v>
       </c>
-      <c r="S41" s="4">
+      <c r="T41" s="4">
         <v>24.090990000000001</v>
       </c>
-      <c r="T41" s="4" t="s">
+      <c r="U41" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U41" s="4" t="s">
+      <c r="V41" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V41" s="4" t="s">
+      <c r="W41" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W41" s="5">
+      <c r="X41" s="5">
         <v>39386</v>
       </c>
-      <c r="X41" s="5"/>
-      <c r="Y41" s="5">
+      <c r="Y41" s="5"/>
+      <c r="Z41" s="5">
         <v>43752</v>
       </c>
-      <c r="Z41" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA41" s="4" t="s">
-        <v>485</v>
+        <v>480</v>
+      </c>
+      <c r="AB41" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>120</v>
       </c>
@@ -5276,44 +5664,47 @@
         <v>220</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="P42" s="4" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="Q42" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="R42" s="4">
+        <v>558</v>
+      </c>
+      <c r="R42" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="S42" s="4">
         <v>90.982176999999993</v>
       </c>
-      <c r="S42" s="4">
+      <c r="T42" s="4">
         <v>24.069662999999998</v>
       </c>
-      <c r="T42" s="4" t="s">
+      <c r="U42" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U42" s="4" t="s">
+      <c r="V42" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V42" s="4" t="s">
+      <c r="W42" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W42" s="5">
+      <c r="X42" s="5">
         <v>44755</v>
       </c>
-      <c r="X42" s="5"/>
-      <c r="Y42" s="5">
+      <c r="Y42" s="5"/>
+      <c r="Z42" s="5">
         <v>44755</v>
       </c>
-      <c r="Z42" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA42" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
+      </c>
+      <c r="AB42" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>122</v>
       </c>
@@ -5357,44 +5748,47 @@
         <v>220</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="P43" s="4" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="Q43" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="R43" s="4">
+        <v>514</v>
+      </c>
+      <c r="R43" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="S43" s="4">
         <v>90.998278299999996</v>
       </c>
-      <c r="S43" s="4">
+      <c r="T43" s="4">
         <v>24.061688199999999</v>
       </c>
-      <c r="T43" s="4" t="s">
+      <c r="U43" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U43" s="4" t="s">
+      <c r="V43" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V43" s="4" t="s">
+      <c r="W43" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W43" s="5">
+      <c r="X43" s="5">
         <v>44811</v>
       </c>
-      <c r="X43" s="5"/>
-      <c r="Y43" s="5">
+      <c r="Y43" s="5"/>
+      <c r="Z43" s="5">
         <v>44811</v>
       </c>
-      <c r="Z43" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA43" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
+      </c>
+      <c r="AB43" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>124</v>
       </c>
@@ -5438,44 +5832,47 @@
         <v>220</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="P44" s="4" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="Q44" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="R44" s="4">
+        <v>515</v>
+      </c>
+      <c r="R44" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="S44" s="4">
         <v>90.986609999999999</v>
       </c>
-      <c r="S44" s="4">
+      <c r="T44" s="4">
         <v>24.044173000000001</v>
       </c>
-      <c r="T44" s="4" t="s">
+      <c r="U44" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U44" s="4" t="s">
+      <c r="V44" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V44" s="4" t="s">
+      <c r="W44" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W44" s="5">
+      <c r="X44" s="5">
         <v>45152</v>
       </c>
-      <c r="X44" s="5"/>
-      <c r="Y44" s="5">
+      <c r="Y44" s="5"/>
+      <c r="Z44" s="5">
         <v>45152</v>
       </c>
-      <c r="Z44" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA44" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
+      </c>
+      <c r="AB44" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>126</v>
       </c>
@@ -5519,44 +5916,47 @@
         <v>220</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="Q45" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="R45" s="4">
+        <v>516</v>
+      </c>
+      <c r="R45" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="S45" s="4">
         <v>90.976799999999997</v>
       </c>
-      <c r="S45" s="4">
+      <c r="T45" s="4">
         <v>24.05611</v>
       </c>
-      <c r="T45" s="4" t="s">
+      <c r="U45" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U45" s="4" t="s">
+      <c r="V45" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V45" s="4" t="s">
+      <c r="W45" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W45" s="5">
+      <c r="X45" s="5">
         <v>40633</v>
       </c>
-      <c r="X45" s="5"/>
-      <c r="Y45" s="5">
+      <c r="Y45" s="5"/>
+      <c r="Z45" s="5">
         <v>43646</v>
       </c>
-      <c r="Z45" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA45" s="4" t="s">
-        <v>485</v>
+        <v>480</v>
+      </c>
+      <c r="AB45" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>128</v>
       </c>
@@ -5600,44 +6000,47 @@
         <v>220</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="Q46" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="R46" s="4">
+        <v>560</v>
+      </c>
+      <c r="R46" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="S46" s="4">
         <v>91.017680999999996</v>
       </c>
-      <c r="S46" s="4">
+      <c r="T46" s="4">
         <v>24.116719</v>
       </c>
-      <c r="T46" s="4" t="s">
+      <c r="U46" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U46" s="4" t="s">
+      <c r="V46" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V46" s="4" t="s">
+      <c r="W46" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W46" s="5">
+      <c r="X46" s="5">
         <v>44889</v>
       </c>
-      <c r="X46" s="5"/>
-      <c r="Y46" s="5">
+      <c r="Y46" s="5"/>
+      <c r="Z46" s="5">
         <v>44889</v>
       </c>
-      <c r="Z46" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA46" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
+      </c>
+      <c r="AB46" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>130</v>
       </c>
@@ -5681,44 +6084,47 @@
         <v>220</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="P47" s="4" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="Q47" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="R47" s="4">
+        <v>517</v>
+      </c>
+      <c r="R47" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="S47" s="4">
         <v>90.975160000000002</v>
       </c>
-      <c r="S47" s="4">
+      <c r="T47" s="4">
         <v>24.092120000000001</v>
       </c>
-      <c r="T47" s="4" t="s">
+      <c r="U47" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U47" s="4" t="s">
+      <c r="V47" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V47" s="4" t="s">
+      <c r="W47" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W47" s="5">
+      <c r="X47" s="5">
         <v>39719</v>
       </c>
-      <c r="X47" s="5"/>
-      <c r="Y47" s="5">
+      <c r="Y47" s="5"/>
+      <c r="Z47" s="5">
         <v>43642</v>
       </c>
-      <c r="Z47" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA47" s="4" t="s">
-        <v>485</v>
+        <v>480</v>
+      </c>
+      <c r="AB47" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>132</v>
       </c>
@@ -5762,44 +6168,47 @@
         <v>220</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="Q48" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="R48" s="4">
+        <v>518</v>
+      </c>
+      <c r="R48" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="S48" s="4">
         <v>90.952029999999993</v>
       </c>
-      <c r="S48" s="4">
+      <c r="T48" s="4">
         <v>24.125260000000001</v>
       </c>
-      <c r="T48" s="4" t="s">
+      <c r="U48" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U48" s="4" t="s">
+      <c r="V48" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V48" s="4" t="s">
+      <c r="W48" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W48" s="5">
+      <c r="X48" s="5">
         <v>43888</v>
       </c>
-      <c r="X48" s="5"/>
-      <c r="Y48" s="5">
+      <c r="Y48" s="5"/>
+      <c r="Z48" s="5">
         <v>43888</v>
       </c>
-      <c r="Z48" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA48" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
+      </c>
+      <c r="AB48" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>134</v>
       </c>
@@ -5843,44 +6252,47 @@
         <v>220</v>
       </c>
       <c r="O49" s="4" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="Q49" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="R49" s="4">
+        <v>561</v>
+      </c>
+      <c r="R49" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="S49" s="4">
         <v>90.98339</v>
       </c>
-      <c r="S49" s="4">
+      <c r="T49" s="4">
         <v>24.076090000000001</v>
       </c>
-      <c r="T49" s="4" t="s">
+      <c r="U49" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U49" s="4" t="s">
+      <c r="V49" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V49" s="4" t="s">
+      <c r="W49" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W49" s="5">
+      <c r="X49" s="5">
         <v>40172</v>
       </c>
-      <c r="X49" s="5"/>
-      <c r="Y49" s="5">
+      <c r="Y49" s="5"/>
+      <c r="Z49" s="5">
         <v>43787</v>
       </c>
-      <c r="Z49" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA49" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
+      </c>
+      <c r="AB49" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>136</v>
       </c>
@@ -5924,44 +6336,47 @@
         <v>220</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="Q50" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="R50" s="4">
+        <v>519</v>
+      </c>
+      <c r="R50" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="S50" s="4">
         <v>90.974086999999997</v>
       </c>
-      <c r="S50" s="4">
+      <c r="T50" s="4">
         <v>24.047618</v>
       </c>
-      <c r="T50" s="4" t="s">
+      <c r="U50" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U50" s="4" t="s">
+      <c r="V50" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V50" s="4" t="s">
+      <c r="W50" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W50" s="5">
+      <c r="X50" s="5">
         <v>44942</v>
       </c>
-      <c r="X50" s="5"/>
-      <c r="Y50" s="5">
+      <c r="Y50" s="5"/>
+      <c r="Z50" s="5">
         <v>44942</v>
       </c>
-      <c r="Z50" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA50" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
+      </c>
+      <c r="AB50" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>138</v>
       </c>
@@ -6005,44 +6420,47 @@
         <v>220</v>
       </c>
       <c r="O51" s="4" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="Q51" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="R51" s="4">
+        <v>520</v>
+      </c>
+      <c r="R51" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="S51" s="4">
         <v>90.978160000000003</v>
       </c>
-      <c r="S51" s="4">
+      <c r="T51" s="4">
         <v>24.062149999999999</v>
       </c>
-      <c r="T51" s="4" t="s">
+      <c r="U51" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U51" s="4" t="s">
+      <c r="V51" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V51" s="4" t="s">
+      <c r="W51" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W51" s="5">
+      <c r="X51" s="5">
         <v>38702</v>
       </c>
-      <c r="X51" s="5"/>
-      <c r="Y51" s="5">
+      <c r="Y51" s="5"/>
+      <c r="Z51" s="5">
         <v>43643</v>
       </c>
-      <c r="Z51" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA51" s="4" t="s">
-        <v>485</v>
+        <v>480</v>
+      </c>
+      <c r="AB51" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>140</v>
       </c>
@@ -6086,44 +6504,47 @@
         <v>220</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P52" s="4" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="Q52" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="R52" s="4">
+        <v>562</v>
+      </c>
+      <c r="R52" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="S52" s="4">
         <v>90.947419999999994</v>
       </c>
-      <c r="S52" s="4">
+      <c r="T52" s="4">
         <v>24.137830000000001</v>
       </c>
-      <c r="T52" s="4" t="s">
+      <c r="U52" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U52" s="4" t="s">
+      <c r="V52" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V52" s="4" t="s">
+      <c r="W52" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W52" s="5">
+      <c r="X52" s="5">
         <v>44587</v>
       </c>
-      <c r="X52" s="5"/>
-      <c r="Y52" s="5">
+      <c r="Y52" s="5"/>
+      <c r="Z52" s="5">
         <v>44587</v>
       </c>
-      <c r="Z52" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA52" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
+      </c>
+      <c r="AB52" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>142</v>
       </c>
@@ -6167,44 +6588,47 @@
         <v>220</v>
       </c>
       <c r="O53" s="4" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="P53" s="4" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="Q53" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="R53" s="4">
+        <v>563</v>
+      </c>
+      <c r="R53" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="S53" s="4">
         <v>90.979552100000006</v>
       </c>
-      <c r="S53" s="4">
+      <c r="T53" s="4">
         <v>24.0474067</v>
       </c>
-      <c r="T53" s="4" t="s">
+      <c r="U53" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U53" s="4" t="s">
+      <c r="V53" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V53" s="4" t="s">
+      <c r="W53" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W53" s="5">
+      <c r="X53" s="5">
         <v>44742</v>
       </c>
-      <c r="X53" s="5"/>
-      <c r="Y53" s="5">
+      <c r="Y53" s="5"/>
+      <c r="Z53" s="5">
         <v>44742</v>
       </c>
-      <c r="Z53" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA53" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
+      </c>
+      <c r="AB53" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>144</v>
       </c>
@@ -6248,44 +6672,47 @@
         <v>220</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="P54" s="4" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="Q54" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="R54" s="4">
+        <v>521</v>
+      </c>
+      <c r="R54" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="S54" s="4">
         <v>91.001829999999998</v>
       </c>
-      <c r="S54" s="4">
+      <c r="T54" s="4">
         <v>24.09479</v>
       </c>
-      <c r="T54" s="4" t="s">
+      <c r="U54" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U54" s="4" t="s">
+      <c r="V54" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V54" s="4" t="s">
+      <c r="W54" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W54" s="5">
+      <c r="X54" s="5">
         <v>42198</v>
       </c>
-      <c r="X54" s="5"/>
-      <c r="Y54" s="5">
+      <c r="Y54" s="5"/>
+      <c r="Z54" s="5">
         <v>43870</v>
       </c>
-      <c r="Z54" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA54" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
+      </c>
+      <c r="AB54" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>146</v>
       </c>
@@ -6329,44 +6756,47 @@
         <v>220</v>
       </c>
       <c r="O55" s="4" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="P55" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="Q55" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="R55" s="4">
+        <v>522</v>
+      </c>
+      <c r="R55" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="S55" s="4">
         <v>90.995272</v>
       </c>
-      <c r="S55" s="4">
+      <c r="T55" s="4">
         <v>24.070359</v>
       </c>
-      <c r="T55" s="4" t="s">
+      <c r="U55" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U55" s="4" t="s">
+      <c r="V55" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V55" s="4" t="s">
+      <c r="W55" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W55" s="5">
+      <c r="X55" s="5">
         <v>44910</v>
       </c>
-      <c r="X55" s="5"/>
-      <c r="Y55" s="5">
+      <c r="Y55" s="5"/>
+      <c r="Z55" s="5">
         <v>44910</v>
       </c>
-      <c r="Z55" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA55" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
+      </c>
+      <c r="AB55" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>148</v>
       </c>
@@ -6410,46 +6840,49 @@
         <v>220</v>
       </c>
       <c r="O56" s="4" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="P56" s="4" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="Q56" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="R56" s="4">
+        <v>564</v>
+      </c>
+      <c r="R56" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="S56" s="4">
         <v>90.984846000000005</v>
       </c>
-      <c r="S56" s="4">
+      <c r="T56" s="4">
         <v>24.042211999999999</v>
       </c>
-      <c r="T56" s="4" t="s">
+      <c r="U56" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U56" s="4" t="s">
+      <c r="V56" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V56" s="4" t="s">
+      <c r="W56" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W56" s="5">
+      <c r="X56" s="5">
         <v>44490</v>
       </c>
-      <c r="X56" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="Y56" s="5">
+      <c r="Y56" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="Z56" s="5">
         <v>44490</v>
       </c>
-      <c r="Z56" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA56" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
+      </c>
+      <c r="AB56" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>150</v>
       </c>
@@ -6493,46 +6926,49 @@
         <v>220</v>
       </c>
       <c r="O57" s="4" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="P57" s="4" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="Q57" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="R57" s="4">
+        <v>565</v>
+      </c>
+      <c r="R57" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="S57" s="4">
         <v>90.968549999999993</v>
       </c>
-      <c r="S57" s="4">
+      <c r="T57" s="4">
         <v>24.129270000000002</v>
       </c>
-      <c r="T57" s="4" t="s">
+      <c r="U57" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U57" s="4" t="s">
+      <c r="V57" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V57" s="4" t="s">
+      <c r="W57" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W57" s="5">
+      <c r="X57" s="5">
         <v>44371</v>
       </c>
-      <c r="X57" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="Y57" s="5">
+      <c r="Y57" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="Z57" s="5">
         <v>44371</v>
       </c>
-      <c r="Z57" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA57" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
+      </c>
+      <c r="AB57" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>152</v>
       </c>
@@ -6576,44 +7012,47 @@
         <v>220</v>
       </c>
       <c r="O58" s="4" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="Q58" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="R58" s="4">
+        <v>523</v>
+      </c>
+      <c r="R58" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="S58" s="4">
         <v>91.016170000000002</v>
       </c>
-      <c r="S58" s="4">
+      <c r="T58" s="4">
         <v>24.081779999999998</v>
       </c>
-      <c r="T58" s="4" t="s">
+      <c r="U58" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U58" s="4" t="s">
+      <c r="V58" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V58" s="4" t="s">
+      <c r="W58" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W58" s="5">
+      <c r="X58" s="5">
         <v>40528</v>
       </c>
-      <c r="X58" s="5"/>
-      <c r="Y58" s="5">
+      <c r="Y58" s="5"/>
+      <c r="Z58" s="5">
         <v>43787</v>
       </c>
-      <c r="Z58" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA58" s="4" t="s">
-        <v>485</v>
+        <v>480</v>
+      </c>
+      <c r="AB58" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
         <v>154</v>
       </c>
@@ -6657,44 +7096,47 @@
         <v>220</v>
       </c>
       <c r="O59" s="4" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="Q59" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="R59" s="4">
+        <v>524</v>
+      </c>
+      <c r="R59" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="S59" s="4">
         <v>90.982619999999997</v>
       </c>
-      <c r="S59" s="4">
+      <c r="T59" s="4">
         <v>24.055409999999998</v>
       </c>
-      <c r="T59" s="4" t="s">
+      <c r="U59" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U59" s="4" t="s">
+      <c r="V59" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V59" s="4" t="s">
+      <c r="W59" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W59" s="5">
+      <c r="X59" s="5">
         <v>39342</v>
       </c>
-      <c r="X59" s="5"/>
-      <c r="Y59" s="5">
+      <c r="Y59" s="5"/>
+      <c r="Z59" s="5">
         <v>43643</v>
       </c>
-      <c r="Z59" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA59" s="4" t="s">
-        <v>485</v>
+        <v>480</v>
+      </c>
+      <c r="AB59" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>156</v>
       </c>
@@ -6738,44 +7180,47 @@
         <v>220</v>
       </c>
       <c r="O60" s="4" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="Q60" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="R60" s="4">
+        <v>567</v>
+      </c>
+      <c r="R60" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="S60" s="4">
         <v>90.983649200000002</v>
       </c>
-      <c r="S60" s="4">
+      <c r="T60" s="4">
         <v>24.100121099999999</v>
       </c>
-      <c r="T60" s="4" t="s">
+      <c r="U60" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U60" s="4" t="s">
+      <c r="V60" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V60" s="4" t="s">
+      <c r="W60" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W60" s="5">
+      <c r="X60" s="5">
         <v>44681</v>
       </c>
-      <c r="X60" s="5"/>
-      <c r="Y60" s="5">
+      <c r="Y60" s="5"/>
+      <c r="Z60" s="5">
         <v>44681</v>
       </c>
-      <c r="Z60" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA60" s="4" t="s">
-        <v>486</v>
+        <v>480</v>
+      </c>
+      <c r="AB60" s="4" t="s">
+        <v>478</v>
       </c>
     </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>158</v>
       </c>
@@ -6819,44 +7264,47 @@
         <v>220</v>
       </c>
       <c r="O61" s="4" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="Q61" s="4" t="s">
-        <v>397</v>
-      </c>
-      <c r="R61" s="4">
+        <v>525</v>
+      </c>
+      <c r="R61" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="S61" s="4">
         <v>90.961969999999994</v>
       </c>
-      <c r="S61" s="4">
+      <c r="T61" s="4">
         <v>24.075569999999999</v>
       </c>
-      <c r="T61" s="4" t="s">
+      <c r="U61" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U61" s="4" t="s">
+      <c r="V61" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V61" s="4" t="s">
+      <c r="W61" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W61" s="5">
+      <c r="X61" s="5">
         <v>43226</v>
       </c>
-      <c r="X61" s="5"/>
-      <c r="Y61" s="5">
+      <c r="Y61" s="5"/>
+      <c r="Z61" s="5">
         <v>43797</v>
       </c>
-      <c r="Z61" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA61" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
+      </c>
+      <c r="AB61" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>160</v>
       </c>
@@ -6900,44 +7348,47 @@
         <v>220</v>
       </c>
       <c r="O62" s="4" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="Q62" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="R62" s="4">
+        <v>568</v>
+      </c>
+      <c r="R62" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="S62" s="4">
         <v>90.984560000000002</v>
       </c>
-      <c r="S62" s="4">
+      <c r="T62" s="4">
         <v>24.048760000000001</v>
       </c>
-      <c r="T62" s="4" t="s">
+      <c r="U62" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U62" s="4" t="s">
+      <c r="V62" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V62" s="4" t="s">
+      <c r="W62" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W62" s="5">
+      <c r="X62" s="5">
         <v>40482</v>
       </c>
-      <c r="X62" s="5"/>
-      <c r="Y62" s="5">
+      <c r="Y62" s="5"/>
+      <c r="Z62" s="5">
         <v>43797</v>
       </c>
-      <c r="Z62" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA62" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
+      </c>
+      <c r="AB62" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
         <v>162</v>
       </c>
@@ -6981,46 +7432,49 @@
         <v>220</v>
       </c>
       <c r="O63" s="4" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="Q63" s="4" t="s">
-        <v>403</v>
-      </c>
-      <c r="R63" s="4">
+        <v>526</v>
+      </c>
+      <c r="R63" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="S63" s="4">
         <v>91.000803000000005</v>
       </c>
-      <c r="S63" s="4">
+      <c r="T63" s="4">
         <v>24.108706000000002</v>
       </c>
-      <c r="T63" s="4" t="s">
+      <c r="U63" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U63" s="4" t="s">
+      <c r="V63" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V63" s="4" t="s">
+      <c r="W63" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W63" s="5">
+      <c r="X63" s="5">
         <v>44413</v>
       </c>
-      <c r="X63" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="Y63" s="5">
+      <c r="Y63" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="Z63" s="5">
         <v>44413</v>
       </c>
-      <c r="Z63" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA63" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
+      </c>
+      <c r="AB63" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>164</v>
       </c>
@@ -7064,46 +7518,49 @@
         <v>220</v>
       </c>
       <c r="O64" s="4" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="Q64" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="R64" s="4">
+        <v>569</v>
+      </c>
+      <c r="R64" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="S64" s="4">
         <v>90.913300000000007</v>
       </c>
-      <c r="S64" s="4">
+      <c r="T64" s="4">
         <v>24.08653</v>
       </c>
-      <c r="T64" s="4" t="s">
+      <c r="U64" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U64" s="4" t="s">
+      <c r="V64" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V64" s="4" t="s">
+      <c r="W64" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W64" s="5">
+      <c r="X64" s="5">
         <v>44407</v>
       </c>
-      <c r="X64" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="Y64" s="5">
+      <c r="Y64" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="Z64" s="5">
         <v>44407</v>
       </c>
-      <c r="Z64" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="AA64" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
+      </c>
+      <c r="AB64" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>166</v>
       </c>
@@ -7147,44 +7604,47 @@
         <v>220</v>
       </c>
       <c r="O65" s="4" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="Q65" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="R65" s="4">
+        <v>570</v>
+      </c>
+      <c r="R65" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="S65" s="4">
         <v>90.872831000000005</v>
       </c>
-      <c r="S65" s="4">
+      <c r="T65" s="4">
         <v>24.271999999999998</v>
       </c>
-      <c r="T65" s="4" t="s">
+      <c r="U65" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U65" s="4" t="s">
+      <c r="V65" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V65" s="4" t="s">
+      <c r="W65" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W65" s="5">
+      <c r="X65" s="5">
         <v>44926</v>
       </c>
-      <c r="X65" s="5"/>
-      <c r="Y65" s="5">
+      <c r="Y65" s="5"/>
+      <c r="Z65" s="5">
         <v>44926</v>
       </c>
-      <c r="Z65" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA65" s="4" t="s">
-        <v>484</v>
+        <v>475</v>
+      </c>
+      <c r="AB65" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="66" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>170</v>
       </c>
@@ -7228,46 +7688,49 @@
         <v>220</v>
       </c>
       <c r="O66" s="4" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="P66" s="4" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="Q66" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="R66" s="4">
+        <v>571</v>
+      </c>
+      <c r="R66" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="S66" s="4">
         <v>90.827849999999998</v>
       </c>
-      <c r="S66" s="4">
+      <c r="T66" s="4">
         <v>24.237269999999999</v>
       </c>
-      <c r="T66" s="4" t="s">
+      <c r="U66" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U66" s="4" t="s">
+      <c r="V66" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V66" s="4" t="s">
+      <c r="W66" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W66" s="5">
+      <c r="X66" s="5">
         <v>44556</v>
       </c>
-      <c r="X66" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="Y66" s="5">
+      <c r="Y66" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="Z66" s="5">
         <v>44556</v>
       </c>
-      <c r="Z66" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA66" s="4" t="s">
-        <v>486</v>
+        <v>475</v>
+      </c>
+      <c r="AB66" s="4" t="s">
+        <v>478</v>
       </c>
     </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
         <v>172</v>
       </c>
@@ -7311,44 +7774,47 @@
         <v>220</v>
       </c>
       <c r="O67" s="4" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="P67" s="4" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="Q67" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="R67" s="4">
+        <v>527</v>
+      </c>
+      <c r="R67" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="S67" s="4">
         <v>90.888949999999994</v>
       </c>
-      <c r="S67" s="4">
+      <c r="T67" s="4">
         <v>24.189299999999999</v>
       </c>
-      <c r="T67" s="4" t="s">
+      <c r="U67" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U67" s="4" t="s">
+      <c r="V67" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V67" s="4" t="s">
+      <c r="W67" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W67" s="5">
+      <c r="X67" s="5">
         <v>39342</v>
       </c>
-      <c r="X67" s="5"/>
-      <c r="Y67" s="5">
+      <c r="Y67" s="5"/>
+      <c r="Z67" s="5">
         <v>43764</v>
       </c>
-      <c r="Z67" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA67" s="4" t="s">
-        <v>485</v>
+        <v>475</v>
+      </c>
+      <c r="AB67" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>176</v>
       </c>
@@ -7392,44 +7858,47 @@
         <v>220</v>
       </c>
       <c r="O68" s="4" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="P68" s="4" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="Q68" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="R68" s="4">
+        <v>528</v>
+      </c>
+      <c r="R68" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="S68" s="4">
         <v>90.93074</v>
       </c>
-      <c r="S68" s="4">
+      <c r="T68" s="4">
         <v>24.16225</v>
       </c>
-      <c r="T68" s="4" t="s">
+      <c r="U68" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U68" s="4" t="s">
+      <c r="V68" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V68" s="4" t="s">
+      <c r="W68" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W68" s="5">
+      <c r="X68" s="5">
         <v>39686</v>
       </c>
-      <c r="X68" s="5"/>
-      <c r="Y68" s="5">
+      <c r="Y68" s="5"/>
+      <c r="Z68" s="5">
         <v>43640</v>
       </c>
-      <c r="Z68" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA68" s="4" t="s">
-        <v>485</v>
+        <v>475</v>
+      </c>
+      <c r="AB68" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="69" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>178</v>
       </c>
@@ -7473,44 +7942,47 @@
         <v>220</v>
       </c>
       <c r="O69" s="4" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="P69" s="4" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="Q69" s="4" t="s">
-        <v>421</v>
-      </c>
-      <c r="R69" s="4">
+        <v>529</v>
+      </c>
+      <c r="R69" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="S69" s="4">
         <v>90.890469999999993</v>
       </c>
-      <c r="S69" s="4">
+      <c r="T69" s="4">
         <v>24.154399999999999</v>
       </c>
-      <c r="T69" s="4" t="s">
+      <c r="U69" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U69" s="4" t="s">
+      <c r="V69" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V69" s="4" t="s">
+      <c r="W69" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W69" s="5">
+      <c r="X69" s="5">
         <v>43248</v>
       </c>
-      <c r="X69" s="5"/>
-      <c r="Y69" s="5">
+      <c r="Y69" s="5"/>
+      <c r="Z69" s="5">
         <v>43871</v>
       </c>
-      <c r="Z69" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA69" s="4" t="s">
-        <v>484</v>
+        <v>475</v>
+      </c>
+      <c r="AB69" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>180</v>
       </c>
@@ -7554,44 +8026,47 @@
         <v>220</v>
       </c>
       <c r="O70" s="4" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="P70" s="4" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="Q70" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="R70" s="4">
+        <v>530</v>
+      </c>
+      <c r="R70" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="S70" s="4">
         <v>90.913970000000006</v>
       </c>
-      <c r="S70" s="4">
+      <c r="T70" s="4">
         <v>24.125399999999999</v>
       </c>
-      <c r="T70" s="4" t="s">
+      <c r="U70" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U70" s="4" t="s">
+      <c r="V70" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V70" s="4" t="s">
+      <c r="W70" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W70" s="5">
+      <c r="X70" s="5">
         <v>39342</v>
       </c>
-      <c r="X70" s="5"/>
-      <c r="Y70" s="5">
+      <c r="Y70" s="5"/>
+      <c r="Z70" s="5">
         <v>43656</v>
       </c>
-      <c r="Z70" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA70" s="4" t="s">
-        <v>485</v>
+        <v>475</v>
+      </c>
+      <c r="AB70" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>182</v>
       </c>
@@ -7635,46 +8110,49 @@
         <v>220</v>
       </c>
       <c r="O71" s="4" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="P71" s="4" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="Q71" s="4" t="s">
-        <v>427</v>
-      </c>
-      <c r="R71" s="4">
+        <v>531</v>
+      </c>
+      <c r="R71" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="S71" s="4">
         <v>90.912379000000001</v>
       </c>
-      <c r="S71" s="4">
+      <c r="T71" s="4">
         <v>24.140432000000001</v>
       </c>
-      <c r="T71" s="4" t="s">
+      <c r="U71" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U71" s="4" t="s">
+      <c r="V71" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V71" s="4" t="s">
+      <c r="W71" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W71" s="5">
+      <c r="X71" s="5">
         <v>44651</v>
       </c>
-      <c r="X71" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="Y71" s="5">
+      <c r="Y71" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="Z71" s="5">
         <v>44651</v>
       </c>
-      <c r="Z71" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA71" s="4" t="s">
-        <v>485</v>
+        <v>475</v>
+      </c>
+      <c r="AB71" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>184</v>
       </c>
@@ -7718,44 +8196,47 @@
         <v>220</v>
       </c>
       <c r="O72" s="4" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="P72" s="4" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="Q72" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="R72" s="4">
+        <v>532</v>
+      </c>
+      <c r="R72" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="S72" s="4">
         <v>90.896026000000006</v>
       </c>
-      <c r="S72" s="4">
+      <c r="T72" s="4">
         <v>24.114674999999998</v>
       </c>
-      <c r="T72" s="4" t="s">
+      <c r="U72" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U72" s="4" t="s">
+      <c r="V72" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V72" s="4" t="s">
+      <c r="W72" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W72" s="5">
+      <c r="X72" s="5">
         <v>45043</v>
       </c>
-      <c r="X72" s="5"/>
-      <c r="Y72" s="5">
+      <c r="Y72" s="5"/>
+      <c r="Z72" s="5">
         <v>45043</v>
       </c>
-      <c r="Z72" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA72" s="4" t="s">
-        <v>484</v>
+        <v>475</v>
+      </c>
+      <c r="AB72" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
         <v>186</v>
       </c>
@@ -7799,44 +8280,47 @@
         <v>220</v>
       </c>
       <c r="O73" s="4" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="P73" s="4" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="Q73" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="R73" s="4">
+        <v>533</v>
+      </c>
+      <c r="R73" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="S73" s="4">
         <v>90.873019999999997</v>
       </c>
-      <c r="S73" s="4">
+      <c r="T73" s="4">
         <v>24.141369999999998</v>
       </c>
-      <c r="T73" s="4" t="s">
+      <c r="U73" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U73" s="4" t="s">
+      <c r="V73" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V73" s="4" t="s">
+      <c r="W73" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W73" s="5">
+      <c r="X73" s="5">
         <v>41788</v>
       </c>
-      <c r="X73" s="5"/>
-      <c r="Y73" s="5">
+      <c r="Y73" s="5"/>
+      <c r="Z73" s="5">
         <v>43787</v>
       </c>
-      <c r="Z73" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA73" s="4" t="s">
-        <v>484</v>
+        <v>475</v>
+      </c>
+      <c r="AB73" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
         <v>188</v>
       </c>
@@ -7880,44 +8364,47 @@
         <v>220</v>
       </c>
       <c r="O74" s="4" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="P74" s="4" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="Q74" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="R74" s="4">
+        <v>534</v>
+      </c>
+      <c r="R74" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="S74" s="4">
         <v>90.931241</v>
       </c>
-      <c r="S74" s="4">
+      <c r="T74" s="4">
         <v>24.154779999999999</v>
       </c>
-      <c r="T74" s="4" t="s">
+      <c r="U74" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U74" s="4" t="s">
+      <c r="V74" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V74" s="4" t="s">
+      <c r="W74" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W74" s="5">
+      <c r="X74" s="5">
         <v>44789</v>
       </c>
-      <c r="X74" s="5"/>
-      <c r="Y74" s="5">
+      <c r="Y74" s="5"/>
+      <c r="Z74" s="5">
         <v>44789</v>
       </c>
-      <c r="Z74" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA74" s="4" t="s">
-        <v>484</v>
+        <v>475</v>
+      </c>
+      <c r="AB74" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>190</v>
       </c>
@@ -7961,44 +8448,47 @@
         <v>220</v>
       </c>
       <c r="O75" s="4" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="P75" s="4" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="Q75" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="R75" s="4">
+        <v>535</v>
+      </c>
+      <c r="R75" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="S75" s="4">
         <v>90.864249999999998</v>
       </c>
-      <c r="S75" s="4">
+      <c r="T75" s="4">
         <v>24.112410000000001</v>
       </c>
-      <c r="T75" s="4" t="s">
+      <c r="U75" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U75" s="4" t="s">
+      <c r="V75" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V75" s="4" t="s">
+      <c r="W75" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W75" s="5">
+      <c r="X75" s="5">
         <v>44742</v>
       </c>
-      <c r="X75" s="5"/>
-      <c r="Y75" s="5">
+      <c r="Y75" s="5"/>
+      <c r="Z75" s="5">
         <v>44742</v>
       </c>
-      <c r="Z75" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA75" s="4" t="s">
-        <v>484</v>
+        <v>475</v>
+      </c>
+      <c r="AB75" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="76" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>192</v>
       </c>
@@ -8042,46 +8532,49 @@
         <v>220</v>
       </c>
       <c r="O76" s="4" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="P76" s="4" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="Q76" s="4" t="s">
-        <v>442</v>
-      </c>
-      <c r="R76" s="4">
+        <v>572</v>
+      </c>
+      <c r="R76" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="S76" s="4">
         <v>90.887770000000003</v>
       </c>
-      <c r="S76" s="4">
+      <c r="T76" s="4">
         <v>24.099589999999999</v>
       </c>
-      <c r="T76" s="4" t="s">
+      <c r="U76" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U76" s="4" t="s">
+      <c r="V76" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V76" s="4" t="s">
+      <c r="W76" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W76" s="5">
+      <c r="X76" s="5">
         <v>44651</v>
       </c>
-      <c r="X76" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="Y76" s="5">
+      <c r="Y76" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="Z76" s="5">
         <v>44651</v>
       </c>
-      <c r="Z76" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA76" s="4" t="s">
-        <v>484</v>
+        <v>475</v>
+      </c>
+      <c r="AB76" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="77" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>194</v>
       </c>
@@ -8125,44 +8618,47 @@
         <v>220</v>
       </c>
       <c r="O77" s="4" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="P77" s="4" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="Q77" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="R77" s="4">
+        <v>536</v>
+      </c>
+      <c r="R77" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="S77" s="4">
         <v>90.906870999999995</v>
       </c>
-      <c r="S77" s="4">
+      <c r="T77" s="4">
         <v>24.100618999999998</v>
       </c>
-      <c r="T77" s="4" t="s">
+      <c r="U77" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U77" s="4" t="s">
+      <c r="V77" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V77" s="4" t="s">
+      <c r="W77" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W77" s="5">
+      <c r="X77" s="5">
         <v>44766</v>
       </c>
-      <c r="X77" s="5"/>
-      <c r="Y77" s="5">
+      <c r="Y77" s="5"/>
+      <c r="Z77" s="5">
         <v>44766</v>
       </c>
-      <c r="Z77" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA77" s="4" t="s">
-        <v>484</v>
+        <v>475</v>
+      </c>
+      <c r="AB77" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>196</v>
       </c>
@@ -8206,44 +8702,47 @@
         <v>220</v>
       </c>
       <c r="O78" s="4" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="P78" s="4" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="Q78" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="R78" s="4">
+        <v>574</v>
+      </c>
+      <c r="R78" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="S78" s="4">
         <v>90.85942</v>
       </c>
-      <c r="S78" s="4">
+      <c r="T78" s="4">
         <v>24.176100000000002</v>
       </c>
-      <c r="T78" s="4" t="s">
+      <c r="U78" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U78" s="4" t="s">
+      <c r="V78" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V78" s="4" t="s">
+      <c r="W78" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W78" s="5">
+      <c r="X78" s="5">
         <v>40908</v>
       </c>
-      <c r="X78" s="5"/>
-      <c r="Y78" s="5">
+      <c r="Y78" s="5"/>
+      <c r="Z78" s="5">
         <v>43787</v>
       </c>
-      <c r="Z78" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA78" s="4" t="s">
-        <v>485</v>
+        <v>475</v>
+      </c>
+      <c r="AB78" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="79" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
         <v>198</v>
       </c>
@@ -8287,44 +8786,47 @@
         <v>220</v>
       </c>
       <c r="O79" s="4" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="P79" s="4" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="Q79" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="R79" s="4">
+        <v>537</v>
+      </c>
+      <c r="R79" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="S79" s="4">
         <v>90.931719999999999</v>
       </c>
-      <c r="S79" s="4">
+      <c r="T79" s="4">
         <v>24.151029999999999</v>
       </c>
-      <c r="T79" s="4" t="s">
+      <c r="U79" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U79" s="4" t="s">
+      <c r="V79" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V79" s="4" t="s">
+      <c r="W79" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W79" s="5">
+      <c r="X79" s="5">
         <v>39070</v>
       </c>
-      <c r="X79" s="5"/>
-      <c r="Y79" s="5">
+      <c r="Y79" s="5"/>
+      <c r="Z79" s="5">
         <v>43646</v>
       </c>
-      <c r="Z79" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA79" s="4" t="s">
-        <v>485</v>
+        <v>475</v>
+      </c>
+      <c r="AB79" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="80" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>200</v>
       </c>
@@ -8368,44 +8870,47 @@
         <v>220</v>
       </c>
       <c r="O80" s="4" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="P80" s="4" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="Q80" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="R80" s="4">
+        <v>575</v>
+      </c>
+      <c r="R80" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="S80" s="4">
         <v>90.939482600000005</v>
       </c>
-      <c r="S80" s="4">
+      <c r="T80" s="4">
         <v>24.1660413</v>
       </c>
-      <c r="T80" s="4" t="s">
+      <c r="U80" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U80" s="4" t="s">
+      <c r="V80" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V80" s="4" t="s">
+      <c r="W80" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W80" s="5">
+      <c r="X80" s="5">
         <v>44712</v>
       </c>
-      <c r="X80" s="5"/>
-      <c r="Y80" s="5">
+      <c r="Y80" s="5"/>
+      <c r="Z80" s="5">
         <v>44712</v>
       </c>
-      <c r="Z80" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA80" s="4" t="s">
-        <v>486</v>
+        <v>475</v>
+      </c>
+      <c r="AB80" s="4" t="s">
+        <v>478</v>
       </c>
     </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
         <v>202</v>
       </c>
@@ -8449,44 +8954,47 @@
         <v>220</v>
       </c>
       <c r="O81" s="4" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="P81" s="4" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="Q81" s="4" t="s">
-        <v>457</v>
-      </c>
-      <c r="R81" s="4">
+        <v>538</v>
+      </c>
+      <c r="R81" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="S81" s="4">
         <v>90.916489999999996</v>
       </c>
-      <c r="S81" s="4">
+      <c r="T81" s="4">
         <v>24.183250000000001</v>
       </c>
-      <c r="T81" s="4" t="s">
+      <c r="U81" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U81" s="4" t="s">
+      <c r="V81" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V81" s="4" t="s">
+      <c r="W81" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W81" s="5">
+      <c r="X81" s="5">
         <v>44208</v>
       </c>
-      <c r="X81" s="5"/>
-      <c r="Y81" s="5">
+      <c r="Y81" s="5"/>
+      <c r="Z81" s="5">
         <v>44208</v>
       </c>
-      <c r="Z81" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA81" s="4" t="s">
-        <v>485</v>
+        <v>475</v>
+      </c>
+      <c r="AB81" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
         <v>204</v>
       </c>
@@ -8530,44 +9038,47 @@
         <v>220</v>
       </c>
       <c r="O82" s="4" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="P82" s="4" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="Q82" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="R82" s="4">
+        <v>576</v>
+      </c>
+      <c r="R82" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="S82" s="4">
         <v>90.917429999999996</v>
       </c>
-      <c r="S82" s="4">
+      <c r="T82" s="4">
         <v>24.160489999999999</v>
       </c>
-      <c r="T82" s="4" t="s">
+      <c r="U82" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U82" s="4" t="s">
+      <c r="V82" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V82" s="4" t="s">
+      <c r="W82" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W82" s="5">
+      <c r="X82" s="5">
         <v>45358</v>
       </c>
-      <c r="X82" s="5"/>
-      <c r="Y82" s="5">
+      <c r="Y82" s="5"/>
+      <c r="Z82" s="5">
         <v>45358</v>
       </c>
-      <c r="Z82" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA82" s="4" t="s">
-        <v>487</v>
+        <v>475</v>
+      </c>
+      <c r="AB82" s="4" t="s">
+        <v>479</v>
       </c>
     </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
         <v>206</v>
       </c>
@@ -8611,44 +9122,47 @@
         <v>220</v>
       </c>
       <c r="O83" s="4" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="P83" s="4" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="Q83" s="4" t="s">
-        <v>463</v>
-      </c>
-      <c r="R83" s="4">
+        <v>539</v>
+      </c>
+      <c r="R83" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="S83" s="4">
         <v>90.925560000000004</v>
       </c>
-      <c r="S83" s="4">
+      <c r="T83" s="4">
         <v>24.14864</v>
       </c>
-      <c r="T83" s="4" t="s">
+      <c r="U83" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U83" s="4" t="s">
+      <c r="V83" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V83" s="4" t="s">
+      <c r="W83" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W83" s="5">
+      <c r="X83" s="5">
         <v>41382</v>
       </c>
-      <c r="X83" s="5"/>
-      <c r="Y83" s="5">
+      <c r="Y83" s="5"/>
+      <c r="Z83" s="5">
         <v>43643</v>
       </c>
-      <c r="Z83" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA83" s="4" t="s">
-        <v>485</v>
+        <v>475</v>
+      </c>
+      <c r="AB83" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
         <v>208</v>
       </c>
@@ -8692,44 +9206,47 @@
         <v>220</v>
       </c>
       <c r="O84" s="4" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="P84" s="4" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="Q84" s="4" t="s">
-        <v>466</v>
-      </c>
-      <c r="R84" s="4">
+        <v>540</v>
+      </c>
+      <c r="R84" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="S84" s="4">
         <v>90.878065000000007</v>
       </c>
-      <c r="S84" s="4">
+      <c r="T84" s="4">
         <v>24.180676999999999</v>
       </c>
-      <c r="T84" s="4" t="s">
+      <c r="U84" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U84" s="4" t="s">
+      <c r="V84" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V84" s="4" t="s">
+      <c r="W84" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W84" s="5">
+      <c r="X84" s="5">
         <v>45169</v>
       </c>
-      <c r="X84" s="5"/>
-      <c r="Y84" s="5">
+      <c r="Y84" s="5"/>
+      <c r="Z84" s="5">
         <v>45169</v>
       </c>
-      <c r="Z84" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA84" s="4" t="s">
-        <v>484</v>
+        <v>475</v>
+      </c>
+      <c r="AB84" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
         <v>210</v>
       </c>
@@ -8773,44 +9290,47 @@
         <v>220</v>
       </c>
       <c r="O85" s="4" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="P85" s="4" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="Q85" s="4" t="s">
-        <v>469</v>
-      </c>
-      <c r="R85" s="4">
+        <v>541</v>
+      </c>
+      <c r="R85" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="S85" s="4">
         <v>90.839150000000004</v>
       </c>
-      <c r="S85" s="4">
+      <c r="T85" s="4">
         <v>24.17248</v>
       </c>
-      <c r="T85" s="4" t="s">
+      <c r="U85" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U85" s="4" t="s">
+      <c r="V85" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V85" s="4" t="s">
+      <c r="W85" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W85" s="5">
+      <c r="X85" s="5">
         <v>43867</v>
       </c>
-      <c r="X85" s="5"/>
-      <c r="Y85" s="5">
+      <c r="Y85" s="5"/>
+      <c r="Z85" s="5">
         <v>43867</v>
       </c>
-      <c r="Z85" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA85" s="4" t="s">
-        <v>484</v>
+        <v>475</v>
+      </c>
+      <c r="AB85" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
         <v>212</v>
       </c>
@@ -8854,44 +9374,47 @@
         <v>220</v>
       </c>
       <c r="O86" s="4" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="P86" s="4" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="Q86" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="R86" s="4">
+        <v>542</v>
+      </c>
+      <c r="R86" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="S86" s="4">
         <v>90.863245000000006</v>
       </c>
-      <c r="S86" s="4">
+      <c r="T86" s="4">
         <v>24.162597000000002</v>
       </c>
-      <c r="T86" s="4" t="s">
+      <c r="U86" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U86" s="4" t="s">
+      <c r="V86" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V86" s="4" t="s">
+      <c r="W86" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W86" s="5">
+      <c r="X86" s="5">
         <v>44773</v>
       </c>
-      <c r="X86" s="5"/>
-      <c r="Y86" s="5">
+      <c r="Y86" s="5"/>
+      <c r="Z86" s="5">
         <v>44773</v>
       </c>
-      <c r="Z86" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA86" s="4" t="s">
-        <v>484</v>
+        <v>475</v>
+      </c>
+      <c r="AB86" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="87" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
         <v>214</v>
       </c>
@@ -8935,44 +9458,47 @@
         <v>220</v>
       </c>
       <c r="O87" s="4" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="P87" s="4" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="Q87" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="R87" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="S87" s="4">
+        <v>90.878680000000003</v>
+      </c>
+      <c r="T87" s="4">
+        <v>24.120480000000001</v>
+      </c>
+      <c r="U87" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="V87" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="W87" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="X87" s="5">
+        <v>44299</v>
+      </c>
+      <c r="Y87" s="5"/>
+      <c r="Z87" s="5">
+        <v>44299</v>
+      </c>
+      <c r="AA87" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="R87" s="4">
-        <v>90.878680000000003</v>
-      </c>
-      <c r="S87" s="4">
-        <v>24.120480000000001</v>
-      </c>
-      <c r="T87" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="U87" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="V87" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="W87" s="5">
-        <v>44299</v>
-      </c>
-      <c r="X87" s="5"/>
-      <c r="Y87" s="5">
-        <v>44299</v>
-      </c>
-      <c r="Z87" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="AA87" s="4" t="s">
-        <v>484</v>
+      <c r="AB87" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="88" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
         <v>216</v>
       </c>
@@ -9016,46 +9542,49 @@
         <v>220</v>
       </c>
       <c r="O88" s="4" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="P88" s="4" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="Q88" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="R88" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="S88" s="4">
+        <v>90.905889999999999</v>
+      </c>
+      <c r="T88" s="4">
+        <v>24.169029999999999</v>
+      </c>
+      <c r="U88" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="V88" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="W88" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="X88" s="5">
+        <v>44658</v>
+      </c>
+      <c r="Y88" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="Z88" s="5">
+        <v>44658</v>
+      </c>
+      <c r="AA88" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="AB88" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="R88" s="4">
-        <v>90.905889999999999</v>
-      </c>
-      <c r="S88" s="4">
-        <v>24.169029999999999</v>
-      </c>
-      <c r="T88" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="U88" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="V88" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="W88" s="5">
-        <v>44658</v>
-      </c>
-      <c r="X88" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="Y88" s="5">
-        <v>44658</v>
-      </c>
-      <c r="Z88" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="AA88" s="4" t="s">
-        <v>486</v>
-      </c>
     </row>
-    <row r="89" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
         <v>218</v>
       </c>
@@ -9099,41 +9628,44 @@
         <v>220</v>
       </c>
       <c r="O89" s="4" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="P89" s="4" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="Q89" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="R89" s="4">
+        <v>579</v>
+      </c>
+      <c r="R89" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="S89" s="4">
         <v>90.933899999999994</v>
       </c>
-      <c r="S89" s="4">
+      <c r="T89" s="4">
         <v>24.158300000000001</v>
       </c>
-      <c r="T89" s="4" t="s">
+      <c r="U89" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U89" s="4" t="s">
+      <c r="V89" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="V89" s="4" t="s">
+      <c r="W89" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="W89" s="5">
+      <c r="X89" s="5">
         <v>44312</v>
       </c>
-      <c r="X89" s="5"/>
-      <c r="Y89" s="5">
+      <c r="Y89" s="5"/>
+      <c r="Z89" s="5">
         <v>44312</v>
       </c>
-      <c r="Z89" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="AA89" s="4" t="s">
-        <v>485</v>
+        <v>475</v>
+      </c>
+      <c r="AB89" s="4" t="s">
+        <v>477</v>
       </c>
     </row>
   </sheetData>
